--- a/Shablon/34460A.xlsx
+++ b/Shablon/34460A.xlsx
@@ -19,16 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="166">
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="161">
   <si>
     <t>Условия проведения калибровки:</t>
   </si>
@@ -573,12 +564,6 @@
   </si>
   <si>
     <t>Поверку провёл:</t>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре акредитованных лиц № РОСС СОБ 3.00231.2014</t>
   </si>
 </sst>
 </file>
@@ -922,54 +907,79 @@
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -977,60 +987,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1344,68 +1329,58 @@
     <col min="1" max="1" width="10.7109375" style="3" customWidth="1"/>
     <col min="2" max="3" width="11.7109375" style="3" customWidth="1"/>
     <col min="4" max="8" width="10.7109375" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="76"/>
+    <col min="9" max="16384" width="9.140625" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="63"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
-        <v>165</v>
-      </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
+      <c r="A5" s="66"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -1418,17 +1393,17 @@
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="72" t="str">
+      <c r="A7" s="77" t="str">
         <f>"Протокол поверки № 10/"&amp;C122&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -1441,29 +1416,29 @@
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="63" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
+      <c r="A9" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
       <c r="D9" s="35" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E9" s="36"/>
-      <c r="F9" s="78" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="78"/>
+      <c r="F9" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="51"/>
       <c r="H9" s="37"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="79" t="s">
-        <v>43</v>
+      <c r="A10" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="52" t="s">
+        <v>40</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
@@ -1471,11 +1446,11 @@
       <c r="H10" s="37"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
+      <c r="A11" s="70" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
       <c r="D11" s="35"/>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
@@ -1483,11 +1458,11 @@
       <c r="H11" s="37"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
+      <c r="A12" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
       <c r="D12" s="38"/>
       <c r="E12" s="36"/>
       <c r="F12" s="36"/>
@@ -1495,13 +1470,13 @@
       <c r="H12" s="37"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="79" t="s">
-        <v>123</v>
+      <c r="A13" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="52" t="s">
+        <v>120</v>
       </c>
       <c r="E13" s="36"/>
       <c r="F13" s="36"/>
@@ -1509,13 +1484,13 @@
       <c r="H13" s="37"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="63" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
+      <c r="A14" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
       <c r="D14" s="39" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
@@ -1523,13 +1498,13 @@
       <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
+      <c r="A15" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
       <c r="D15" s="35" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E15" s="36"/>
       <c r="F15" s="36"/>
@@ -1537,104 +1512,104 @@
       <c r="H15" s="37"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="80"/>
+      <c r="B16" s="53"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="64"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="70"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="69" t="s">
+      <c r="B19" s="72"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="65"/>
+      <c r="F19" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69" t="s">
+      <c r="G19" s="69"/>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="69"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="65"/>
+      <c r="F20" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="81"/>
-      <c r="F19" s="55" t="s">
+      <c r="G20" s="69"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="56"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="71" t="s">
+      <c r="B21" s="72"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="76"/>
+      <c r="F21" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="81" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20" s="81"/>
-      <c r="F20" s="55" t="s">
+      <c r="G21" s="69"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="56"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="57" t="s">
+      <c r="B22" s="72"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="67"/>
-      <c r="F21" s="55" t="s">
+      <c r="G22" s="69"/>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="72"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="56"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="56"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="56"/>
+      <c r="G23" s="69"/>
       <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1649,7 +1624,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
@@ -1671,17 +1646,17 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1693,7 +1668,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -1704,50 +1679,50 @@
       <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="G31" s="53"/>
+      <c r="A31" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="57"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="53"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
       <c r="F32" s="43" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="53" t="s">
-        <v>127</v>
+      <c r="A33" s="57" t="s">
+        <v>124</v>
       </c>
       <c r="B33" s="49">
         <v>100</v>
       </c>
-      <c r="C33" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="82" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="64" t="s">
-        <v>124</v>
+      <c r="C33" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>121</v>
       </c>
       <c r="F33" s="47">
         <f>100-0.0155</f>
@@ -1759,15 +1734,15 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="53"/>
+      <c r="A34" s="57"/>
       <c r="B34" s="49">
         <v>-100</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="64"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="58"/>
       <c r="F34" s="47">
         <f>-100-0.0155</f>
         <v>-100.0155</v>
@@ -1778,20 +1753,20 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
-        <v>128</v>
+      <c r="A35" s="57" t="s">
+        <v>125</v>
       </c>
       <c r="B35" s="49">
         <v>1</v>
       </c>
-      <c r="C35" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" s="82" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="65" t="s">
-        <v>125</v>
+      <c r="C35" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="61" t="s">
+        <v>122</v>
       </c>
       <c r="F35" s="40">
         <f>1-0.00009</f>
@@ -1803,15 +1778,15 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="53"/>
+      <c r="A36" s="57"/>
       <c r="B36" s="49">
         <v>-1</v>
       </c>
-      <c r="C36" s="64"/>
-      <c r="D36" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="65"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="61"/>
       <c r="F36" s="40">
         <f>-1-0.00009</f>
         <v>-1.0000899999999999</v>
@@ -1822,17 +1797,17 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
-        <v>129</v>
+      <c r="A37" s="57" t="s">
+        <v>126</v>
       </c>
       <c r="B37" s="49">
         <v>4</v>
       </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="82" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="65"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="61"/>
       <c r="F37" s="40">
         <f>4-0.00035</f>
         <v>3.9996499999999999</v>
@@ -1843,15 +1818,15 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="53"/>
+      <c r="A38" s="57"/>
       <c r="B38" s="49">
         <v>10</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="82" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="65"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="61"/>
       <c r="F38" s="47">
         <f>10-0.0008</f>
         <v>9.9992000000000001</v>
@@ -1862,15 +1837,15 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="53"/>
+      <c r="A39" s="57"/>
       <c r="B39" s="49">
         <v>-10</v>
       </c>
-      <c r="C39" s="64"/>
-      <c r="D39" s="82" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="65"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="61"/>
       <c r="F39" s="47">
         <f>-10-0.0008</f>
         <v>-10.0008</v>
@@ -1881,17 +1856,17 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
-        <v>130</v>
+      <c r="A40" s="57" t="s">
+        <v>127</v>
       </c>
       <c r="B40" s="49">
         <v>100</v>
       </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="82" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="65"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="61"/>
       <c r="F40" s="47">
         <f>100-0.0091</f>
         <v>99.990899999999996</v>
@@ -1902,15 +1877,15 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="53"/>
+      <c r="A41" s="57"/>
       <c r="B41" s="49">
         <v>-100</v>
       </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="82" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="65"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="61"/>
       <c r="F41" s="47">
         <f>-100-0.0091</f>
         <v>-100.0091</v>
@@ -1921,17 +1896,17 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="60" t="s">
-        <v>131</v>
+      <c r="A42" s="81" t="s">
+        <v>128</v>
       </c>
       <c r="B42" s="49">
         <v>1000</v>
       </c>
-      <c r="C42" s="64"/>
-      <c r="D42" s="82" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="65"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="61"/>
       <c r="F42" s="48">
         <f>1000-0.095</f>
         <v>999.90499999999997</v>
@@ -1942,15 +1917,15 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="60"/>
+      <c r="A43" s="81"/>
       <c r="B43" s="49">
         <v>-500</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="82" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="65"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="61"/>
       <c r="F43" s="47">
         <f>-500-0.0525</f>
         <v>-500.05250000000001</v>
@@ -1962,7 +1937,7 @@
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -1973,57 +1948,57 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B46" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="53"/>
-      <c r="G46" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="H46" s="53"/>
+      <c r="A46" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="H46" s="57"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
       <c r="G47" s="43" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H47" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" s="61">
+      <c r="A48" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" s="82">
         <v>100</v>
       </c>
-      <c r="C48" s="52" t="s">
-        <v>124</v>
+      <c r="C48" s="83" t="s">
+        <v>121</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="83" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" s="52" t="s">
-        <v>124</v>
+        <v>15</v>
+      </c>
+      <c r="E48" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="83" t="s">
+        <v>121</v>
       </c>
       <c r="G48" s="40">
         <f>100-0.12</f>
@@ -2035,16 +2010,16 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="62"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="52"/>
+      <c r="A49" s="84"/>
+      <c r="B49" s="82"/>
+      <c r="C49" s="83"/>
       <c r="D49" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="83" t="s">
-        <v>61</v>
-      </c>
-      <c r="F49" s="52"/>
+        <v>17</v>
+      </c>
+      <c r="E49" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="83"/>
       <c r="G49" s="47">
         <f>100-0.2</f>
         <v>99.8</v>
@@ -2055,16 +2030,16 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="62"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="52"/>
+      <c r="A50" s="84"/>
+      <c r="B50" s="82"/>
+      <c r="C50" s="83"/>
       <c r="D50" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="F50" s="52"/>
+        <v>22</v>
+      </c>
+      <c r="E50" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="83"/>
       <c r="G50" s="47">
         <f>100-4.5</f>
         <v>95.5</v>
@@ -2075,23 +2050,23 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="B51" s="61">
+      <c r="A51" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="82">
         <v>1</v>
       </c>
-      <c r="C51" s="52" t="s">
-        <v>125</v>
+      <c r="C51" s="83" t="s">
+        <v>122</v>
       </c>
       <c r="D51" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="83" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" s="52" t="s">
-        <v>125</v>
+        <v>15</v>
+      </c>
+      <c r="E51" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="83" t="s">
+        <v>122</v>
       </c>
       <c r="G51" s="47">
         <f>1-0.0012</f>
@@ -2103,16 +2078,16 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="54"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="52"/>
+      <c r="A52" s="60"/>
+      <c r="B52" s="82"/>
+      <c r="C52" s="83"/>
       <c r="D52" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="52"/>
+        <v>17</v>
+      </c>
+      <c r="E52" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="83"/>
       <c r="G52" s="48">
         <f>1-0.002</f>
         <v>0.998</v>
@@ -2123,16 +2098,16 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="54"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="52"/>
+      <c r="A53" s="60"/>
+      <c r="B53" s="82"/>
+      <c r="C53" s="83"/>
       <c r="D53" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="F53" s="52"/>
+        <v>22</v>
+      </c>
+      <c r="E53" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="83"/>
       <c r="G53" s="48">
         <f>1-0.045</f>
         <v>0.95499999999999996</v>
@@ -2143,23 +2118,23 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="54" t="s">
-        <v>129</v>
+      <c r="A54" s="60" t="s">
+        <v>126</v>
       </c>
       <c r="B54" s="46">
         <v>30</v>
       </c>
       <c r="C54" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D54" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="83" t="s">
-        <v>66</v>
+        <v>121</v>
+      </c>
+      <c r="D54" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="55" t="s">
+        <v>63</v>
       </c>
       <c r="F54" s="46" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G54" s="48">
         <f>30-0.003</f>
@@ -2171,19 +2146,19 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="54"/>
+      <c r="A55" s="60"/>
       <c r="B55" s="46">
         <v>1</v>
       </c>
-      <c r="C55" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="D55" s="54"/>
-      <c r="E55" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="F55" s="54" t="s">
-        <v>125</v>
+      <c r="C55" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" s="60"/>
+      <c r="E55" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="60" t="s">
+        <v>122</v>
       </c>
       <c r="G55" s="47">
         <f>1-0.0039</f>
@@ -2195,18 +2170,18 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="54"/>
-      <c r="B56" s="54">
+      <c r="A56" s="60"/>
+      <c r="B56" s="60">
         <v>10</v>
       </c>
-      <c r="C56" s="54"/>
+      <c r="C56" s="60"/>
       <c r="D56" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="F56" s="54"/>
+        <v>16</v>
+      </c>
+      <c r="E56" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="60"/>
       <c r="G56" s="48">
         <f>10-0.012</f>
         <v>9.9879999999999995</v>
@@ -2217,16 +2192,16 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="54"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="54"/>
+      <c r="A57" s="60"/>
+      <c r="B57" s="60"/>
+      <c r="C57" s="60"/>
       <c r="D57" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" s="83" t="s">
-        <v>69</v>
-      </c>
-      <c r="F57" s="54"/>
+        <v>19</v>
+      </c>
+      <c r="E57" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57" s="60"/>
       <c r="G57" s="48">
         <f>10-0.012</f>
         <v>9.9879999999999995</v>
@@ -2237,16 +2212,16 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="54"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="54"/>
+      <c r="A58" s="60"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="60"/>
       <c r="D58" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="83" t="s">
-        <v>70</v>
-      </c>
-      <c r="F58" s="54"/>
+        <v>20</v>
+      </c>
+      <c r="E58" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="F58" s="60"/>
       <c r="G58" s="48">
         <f>10-0.012</f>
         <v>9.9879999999999995</v>
@@ -2257,16 +2232,16 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="54"/>
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
+      <c r="A59" s="60"/>
+      <c r="B59" s="60"/>
+      <c r="C59" s="60"/>
       <c r="D59" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="83" t="s">
-        <v>71</v>
-      </c>
-      <c r="F59" s="54"/>
+        <v>17</v>
+      </c>
+      <c r="E59" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="60"/>
       <c r="G59" s="45">
         <f>10-0.02</f>
         <v>9.98</v>
@@ -2277,16 +2252,16 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
+      <c r="A60" s="60"/>
+      <c r="B60" s="60"/>
+      <c r="C60" s="60"/>
       <c r="D60" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="83" t="s">
-        <v>72</v>
-      </c>
-      <c r="F60" s="54"/>
+        <v>21</v>
+      </c>
+      <c r="E60" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60" s="60"/>
       <c r="G60" s="48">
         <f>10-0.071</f>
         <v>9.9290000000000003</v>
@@ -2297,16 +2272,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="54"/>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
+      <c r="A61" s="60"/>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
       <c r="D61" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="F61" s="54"/>
+        <v>22</v>
+      </c>
+      <c r="E61" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="F61" s="60"/>
       <c r="G61" s="45">
         <f>10-0.45</f>
         <v>9.5500000000000007</v>
@@ -2317,23 +2292,23 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="B62" s="54">
+      <c r="A62" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="60">
         <v>100</v>
       </c>
-      <c r="C62" s="54" t="s">
-        <v>125</v>
+      <c r="C62" s="60" t="s">
+        <v>122</v>
       </c>
       <c r="D62" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="83" t="s">
-        <v>74</v>
-      </c>
-      <c r="F62" s="54" t="s">
-        <v>125</v>
+        <v>15</v>
+      </c>
+      <c r="E62" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="60" t="s">
+        <v>122</v>
       </c>
       <c r="G62" s="45">
         <f>100-0.12</f>
@@ -2345,16 +2320,16 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="54"/>
-      <c r="B63" s="54"/>
-      <c r="C63" s="54"/>
+      <c r="A63" s="60"/>
+      <c r="B63" s="60"/>
+      <c r="C63" s="60"/>
       <c r="D63" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="83" t="s">
-        <v>75</v>
-      </c>
-      <c r="F63" s="54"/>
+        <v>17</v>
+      </c>
+      <c r="E63" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="60"/>
       <c r="G63" s="49">
         <f>100-0.2</f>
         <v>99.8</v>
@@ -2365,18 +2340,18 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54"/>
+      <c r="A64" s="60"/>
       <c r="B64" s="46">
         <v>70</v>
       </c>
-      <c r="C64" s="54"/>
+      <c r="C64" s="60"/>
       <c r="D64" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="F64" s="54"/>
+        <v>22</v>
+      </c>
+      <c r="E64" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="F64" s="60"/>
       <c r="G64" s="49">
         <f>70-3.3</f>
         <v>66.7</v>
@@ -2387,23 +2362,23 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="54" t="s">
-        <v>148</v>
+      <c r="A65" s="60" t="s">
+        <v>145</v>
       </c>
       <c r="B65" s="46">
         <v>750</v>
       </c>
-      <c r="C65" s="54" t="s">
-        <v>125</v>
+      <c r="C65" s="60" t="s">
+        <v>122</v>
       </c>
       <c r="D65" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="F65" s="54" t="s">
-        <v>125</v>
+        <v>15</v>
+      </c>
+      <c r="E65" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" s="60" t="s">
+        <v>122</v>
       </c>
       <c r="G65" s="49">
         <f>750-0.9</f>
@@ -2415,18 +2390,18 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="54"/>
+      <c r="A66" s="60"/>
       <c r="B66" s="46">
         <v>210</v>
       </c>
-      <c r="C66" s="54"/>
+      <c r="C66" s="60"/>
       <c r="D66" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="F66" s="54"/>
+        <v>17</v>
+      </c>
+      <c r="E66" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="60"/>
       <c r="G66" s="45">
         <f>210-0.69</f>
         <v>209.31</v>
@@ -2437,18 +2412,18 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="54"/>
+      <c r="A67" s="60"/>
       <c r="B67" s="46">
         <v>70</v>
       </c>
-      <c r="C67" s="54"/>
+      <c r="C67" s="60"/>
       <c r="D67" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="F67" s="54"/>
+        <v>22</v>
+      </c>
+      <c r="E67" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" s="60"/>
       <c r="G67" s="49">
         <f>70-6.6</f>
         <v>63.4</v>
@@ -2468,7 +2443,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B69" s="12"/>
       <c r="C69" s="13"/>
@@ -2477,50 +2452,50 @@
       <c r="F69" s="16"/>
     </row>
     <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C70" s="53"/>
-      <c r="D70" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="E70" s="53"/>
-      <c r="F70" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="G70" s="53"/>
+      <c r="A70" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="G70" s="57"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="53"/>
-      <c r="B71" s="53"/>
-      <c r="C71" s="53"/>
-      <c r="D71" s="53"/>
-      <c r="E71" s="53"/>
+      <c r="A71" s="57"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
       <c r="F71" s="43" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G71" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="46" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B72" s="46">
         <v>100</v>
       </c>
       <c r="C72" s="44" t="s">
-        <v>157</v>
-      </c>
-      <c r="D72" s="83" t="s">
-        <v>80</v>
+        <v>154</v>
+      </c>
+      <c r="D72" s="55" t="s">
+        <v>77</v>
       </c>
       <c r="E72" s="44" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F72" s="48">
         <f>100-0.075</f>
@@ -2533,19 +2508,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="46" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B73" s="46">
         <v>1</v>
       </c>
-      <c r="C73" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="D73" s="83" t="s">
-        <v>81</v>
-      </c>
-      <c r="E73" s="64" t="s">
-        <v>156</v>
+      <c r="C73" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="D73" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="58" t="s">
+        <v>153</v>
       </c>
       <c r="F73" s="40">
         <f>1-0.00056</f>
@@ -2558,16 +2533,16 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="46" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B74" s="46">
         <v>10</v>
       </c>
-      <c r="C74" s="64"/>
-      <c r="D74" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="E74" s="64"/>
+      <c r="C74" s="58"/>
+      <c r="D74" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="E74" s="58"/>
       <c r="F74" s="48">
         <f>10-0.007</f>
         <v>9.9930000000000003</v>
@@ -2579,16 +2554,16 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="46" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B75" s="46">
         <v>100</v>
       </c>
-      <c r="C75" s="64"/>
-      <c r="D75" s="83" t="s">
-        <v>83</v>
-      </c>
-      <c r="E75" s="64"/>
+      <c r="C75" s="58"/>
+      <c r="D75" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E75" s="58"/>
       <c r="F75" s="48">
         <f>100-0.055</f>
         <v>99.944999999999993</v>
@@ -2600,19 +2575,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="46" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B76" s="46">
         <v>1</v>
       </c>
-      <c r="C76" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="D76" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="E76" s="64" t="s">
-        <v>149</v>
+      <c r="C76" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="D76" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="E76" s="58" t="s">
+        <v>146</v>
       </c>
       <c r="F76" s="47">
         <f>1-0.0011</f>
@@ -2625,16 +2600,16 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="46" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B77" s="46">
         <v>2</v>
       </c>
-      <c r="C77" s="64"/>
-      <c r="D77" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="E77" s="64"/>
+      <c r="C77" s="58"/>
+      <c r="D77" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" s="58"/>
       <c r="F77" s="47">
         <f>2-0.0046</f>
         <v>1.9954000000000001</v>
@@ -2654,7 +2629,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B79" s="11"/>
       <c r="C79" s="13"/>
@@ -2663,141 +2638,141 @@
       <c r="F79" s="16"/>
     </row>
     <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="E80" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="H80" s="53"/>
+      <c r="A80" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B80" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="57"/>
+      <c r="D80" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" s="57"/>
+      <c r="G80" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="H80" s="57"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="53"/>
-      <c r="B81" s="53"/>
-      <c r="C81" s="53"/>
-      <c r="D81" s="53"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
+      <c r="A81" s="57"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
       <c r="G81" s="43" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H81" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="54" t="s">
-        <v>155</v>
-      </c>
-      <c r="B82" s="54">
+      <c r="A82" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="60">
         <v>100</v>
       </c>
-      <c r="C82" s="64" t="s">
-        <v>157</v>
+      <c r="C82" s="58" t="s">
+        <v>154</v>
       </c>
       <c r="D82" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="F82" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="G82" s="73">
+        <v>15</v>
+      </c>
+      <c r="E82" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="F82" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="G82" s="59">
         <f>100-0.14</f>
         <v>99.86</v>
       </c>
-      <c r="H82" s="73">
+      <c r="H82" s="59">
         <f>100+0.14</f>
         <v>100.14</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="54"/>
-      <c r="B83" s="54"/>
-      <c r="C83" s="64"/>
+      <c r="A83" s="60"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="58"/>
       <c r="D83" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E83" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="F83" s="64"/>
-      <c r="G83" s="73"/>
-      <c r="H83" s="73"/>
+        <v>23</v>
+      </c>
+      <c r="E83" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="F83" s="58"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="54" t="s">
-        <v>154</v>
-      </c>
-      <c r="B84" s="54">
+      <c r="A84" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="B84" s="60">
         <v>1</v>
       </c>
-      <c r="C84" s="54" t="s">
-        <v>156</v>
+      <c r="C84" s="60" t="s">
+        <v>153</v>
       </c>
       <c r="D84" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" s="83" t="s">
-        <v>88</v>
-      </c>
-      <c r="F84" s="54" t="s">
-        <v>156</v>
-      </c>
-      <c r="G84" s="65">
+        <v>15</v>
+      </c>
+      <c r="E84" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F84" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="G84" s="61">
         <f>1-0.0014</f>
         <v>0.99860000000000004</v>
       </c>
-      <c r="H84" s="54">
+      <c r="H84" s="60">
         <f>1+0.0014</f>
         <v>1.0014000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="54"/>
-      <c r="B85" s="54"/>
-      <c r="C85" s="54"/>
+      <c r="A85" s="60"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
       <c r="D85" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E85" s="83" t="s">
-        <v>89</v>
-      </c>
-      <c r="F85" s="54"/>
-      <c r="G85" s="65"/>
-      <c r="H85" s="54"/>
+        <v>23</v>
+      </c>
+      <c r="E85" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="F85" s="60"/>
+      <c r="G85" s="61"/>
+      <c r="H85" s="60"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="54" t="s">
-        <v>153</v>
+      <c r="A86" s="60" t="s">
+        <v>150</v>
       </c>
       <c r="B86" s="46">
         <v>100</v>
       </c>
       <c r="C86" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="D86" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E86" s="83" t="s">
-        <v>90</v>
+        <v>154</v>
+      </c>
+      <c r="D86" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="55" t="s">
+        <v>87</v>
       </c>
       <c r="F86" s="46" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G86" s="49">
         <f>100-4.1</f>
@@ -2809,19 +2784,19 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="54"/>
+      <c r="A87" s="60"/>
       <c r="B87" s="46">
         <v>1</v>
       </c>
-      <c r="C87" s="54" t="s">
-        <v>156</v>
-      </c>
-      <c r="D87" s="54"/>
-      <c r="E87" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="F87" s="54" t="s">
-        <v>156</v>
+      <c r="C87" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="D87" s="60"/>
+      <c r="E87" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="F87" s="60" t="s">
+        <v>153</v>
       </c>
       <c r="G87" s="48">
         <f>1-0.005</f>
@@ -2833,190 +2808,190 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="54"/>
-      <c r="B88" s="54">
+      <c r="A88" s="60"/>
+      <c r="B88" s="60">
         <v>10</v>
       </c>
-      <c r="C88" s="54"/>
-      <c r="D88" s="54"/>
-      <c r="E88" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="F88" s="54"/>
-      <c r="G88" s="74">
+      <c r="C88" s="60"/>
+      <c r="D88" s="60"/>
+      <c r="E88" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="F88" s="60"/>
+      <c r="G88" s="62">
         <f>10-0.014</f>
         <v>9.9860000000000007</v>
       </c>
-      <c r="H88" s="54">
+      <c r="H88" s="60">
         <f>10+0.014</f>
         <v>10.013999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="54"/>
-      <c r="B89" s="54"/>
-      <c r="C89" s="54"/>
+      <c r="A89" s="60"/>
+      <c r="B89" s="60"/>
+      <c r="C89" s="60"/>
       <c r="D89" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E89" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="F89" s="54"/>
-      <c r="G89" s="74"/>
-      <c r="H89" s="54"/>
+        <v>23</v>
+      </c>
+      <c r="E89" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="F89" s="60"/>
+      <c r="G89" s="62"/>
+      <c r="H89" s="60"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="B90" s="54">
+      <c r="A90" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B90" s="60">
         <v>100</v>
       </c>
-      <c r="C90" s="54" t="s">
-        <v>156</v>
+      <c r="C90" s="60" t="s">
+        <v>153</v>
       </c>
       <c r="D90" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="F90" s="54" t="s">
-        <v>156</v>
-      </c>
-      <c r="G90" s="73">
+        <v>16</v>
+      </c>
+      <c r="E90" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="G90" s="59">
         <f>100-0.14</f>
         <v>99.86</v>
       </c>
-      <c r="H90" s="54">
+      <c r="H90" s="60">
         <f>100+0.14</f>
         <v>100.14</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="54"/>
-      <c r="B91" s="54"/>
-      <c r="C91" s="54"/>
+      <c r="A91" s="60"/>
+      <c r="B91" s="60"/>
+      <c r="C91" s="60"/>
       <c r="D91" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E91" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="F91" s="54"/>
-      <c r="G91" s="73"/>
-      <c r="H91" s="54"/>
+        <v>15</v>
+      </c>
+      <c r="E91" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="F91" s="60"/>
+      <c r="G91" s="59"/>
+      <c r="H91" s="60"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="54"/>
-      <c r="B92" s="54"/>
-      <c r="C92" s="54"/>
+      <c r="A92" s="60"/>
+      <c r="B92" s="60"/>
+      <c r="C92" s="60"/>
       <c r="D92" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E92" s="83" t="s">
-        <v>96</v>
-      </c>
-      <c r="F92" s="54"/>
-      <c r="G92" s="73"/>
-      <c r="H92" s="54"/>
+        <v>23</v>
+      </c>
+      <c r="E92" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="F92" s="60"/>
+      <c r="G92" s="59"/>
+      <c r="H92" s="60"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="B93" s="54">
+      <c r="A93" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="B93" s="60">
         <v>1</v>
       </c>
-      <c r="C93" s="54" t="s">
-        <v>149</v>
+      <c r="C93" s="60" t="s">
+        <v>146</v>
       </c>
       <c r="D93" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E93" s="83" t="s">
-        <v>97</v>
-      </c>
-      <c r="F93" s="54" t="s">
-        <v>149</v>
-      </c>
-      <c r="G93" s="65">
+        <v>15</v>
+      </c>
+      <c r="E93" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="F93" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="G93" s="61">
         <f>1-0.0014</f>
         <v>0.99860000000000004</v>
       </c>
-      <c r="H93" s="54">
+      <c r="H93" s="60">
         <f>1+0.0014</f>
         <v>1.0014000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="54"/>
-      <c r="B94" s="54"/>
-      <c r="C94" s="54"/>
+      <c r="A94" s="60"/>
+      <c r="B94" s="60"/>
+      <c r="C94" s="60"/>
       <c r="D94" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E94" s="83" t="s">
-        <v>98</v>
-      </c>
-      <c r="F94" s="54"/>
-      <c r="G94" s="65"/>
-      <c r="H94" s="54"/>
+        <v>23</v>
+      </c>
+      <c r="E94" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="F94" s="60"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="60"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="54" t="s">
-        <v>151</v>
-      </c>
-      <c r="B95" s="54">
+      <c r="A95" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="B95" s="60">
         <v>2</v>
       </c>
-      <c r="C95" s="54" t="s">
-        <v>149</v>
+      <c r="C95" s="60" t="s">
+        <v>146</v>
       </c>
       <c r="D95" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E95" s="83" t="s">
-        <v>99</v>
-      </c>
-      <c r="F95" s="54" t="s">
-        <v>149</v>
-      </c>
-      <c r="G95" s="65">
+        <v>15</v>
+      </c>
+      <c r="E95" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="F95" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="G95" s="61">
         <f>2-0.0058</f>
         <v>1.9942</v>
       </c>
-      <c r="H95" s="54">
+      <c r="H95" s="60">
         <f>2+0.0058</f>
         <v>2.0057999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="54"/>
-      <c r="B96" s="54"/>
-      <c r="C96" s="54"/>
+      <c r="A96" s="60"/>
+      <c r="B96" s="60"/>
+      <c r="C96" s="60"/>
       <c r="D96" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E96" s="83" t="s">
-        <v>100</v>
-      </c>
-      <c r="F96" s="54"/>
-      <c r="G96" s="65"/>
-      <c r="H96" s="54"/>
+        <v>23</v>
+      </c>
+      <c r="E96" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="F96" s="60"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="60"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="11"/>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
-      <c r="D97" s="84"/>
-      <c r="E97" s="84"/>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
       <c r="F97" s="16"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
@@ -3025,57 +3000,57 @@
       <c r="F98" s="16"/>
     </row>
     <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B99" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="C99" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="53"/>
-      <c r="E99" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" s="53"/>
-      <c r="G99" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="H99" s="53"/>
+      <c r="A99" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B99" s="80" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="57"/>
+      <c r="G99" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="H99" s="57"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="53"/>
-      <c r="B100" s="68"/>
-      <c r="C100" s="53"/>
-      <c r="D100" s="53"/>
-      <c r="E100" s="53"/>
-      <c r="F100" s="53"/>
+      <c r="A100" s="57"/>
+      <c r="B100" s="80"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
       <c r="G100" s="43" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H100" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="43" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B101" s="43" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C101" s="22">
         <v>10</v>
       </c>
       <c r="D101" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E101" s="83" t="s">
-        <v>101</v>
+        <v>132</v>
+      </c>
+      <c r="E101" s="55" t="s">
+        <v>98</v>
       </c>
       <c r="F101" s="44" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G101" s="48">
         <f>10-0.003</f>
@@ -3088,22 +3063,22 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="43" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B102" s="43" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C102" s="22">
         <v>300</v>
       </c>
       <c r="D102" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="E102" s="83" t="s">
-        <v>102</v>
+        <v>133</v>
+      </c>
+      <c r="E102" s="55" t="s">
+        <v>99</v>
       </c>
       <c r="F102" s="44" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G102" s="45">
         <f>300-0.36</f>
@@ -3124,7 +3099,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
@@ -3134,7 +3109,7 @@
     </row>
     <row r="105" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B105" s="18"/>
       <c r="C105" s="18"/>
@@ -3143,50 +3118,50 @@
       <c r="F105" s="21"/>
     </row>
     <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B106" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C106" s="53"/>
-      <c r="D106" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E106" s="53"/>
-      <c r="F106" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="G106" s="53"/>
+      <c r="A106" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C106" s="57"/>
+      <c r="D106" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="57"/>
+      <c r="F106" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="G106" s="57"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="53"/>
-      <c r="B107" s="53"/>
-      <c r="C107" s="53"/>
-      <c r="D107" s="53"/>
-      <c r="E107" s="53"/>
+      <c r="A107" s="57"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="57"/>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
       <c r="F107" s="43" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G107" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B108" s="22">
         <v>100</v>
       </c>
       <c r="C108" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="D108" s="83" t="s">
-        <v>103</v>
+        <v>143</v>
+      </c>
+      <c r="D108" s="55" t="s">
+        <v>100</v>
       </c>
       <c r="E108" s="44" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F108" s="48">
         <f>100-0.021</f>
@@ -3199,19 +3174,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B109" s="22">
         <v>1</v>
       </c>
-      <c r="C109" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="D109" s="83" t="s">
-        <v>104</v>
-      </c>
-      <c r="E109" s="64" t="s">
-        <v>147</v>
+      <c r="C109" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="D109" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="E109" s="58" t="s">
+        <v>144</v>
       </c>
       <c r="F109" s="40">
         <f>1-0.00015</f>
@@ -3224,16 +3199,16 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B110" s="22">
         <v>10</v>
       </c>
-      <c r="C110" s="64"/>
-      <c r="D110" s="83" t="s">
-        <v>105</v>
-      </c>
-      <c r="E110" s="64"/>
+      <c r="C110" s="58"/>
+      <c r="D110" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="E110" s="58"/>
       <c r="F110" s="47">
         <f>10-0.0015</f>
         <v>9.9984999999999999</v>
@@ -3245,16 +3220,16 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B111" s="22">
         <v>100</v>
       </c>
-      <c r="C111" s="64"/>
-      <c r="D111" s="83" t="s">
-        <v>106</v>
-      </c>
-      <c r="E111" s="64"/>
+      <c r="C111" s="58"/>
+      <c r="D111" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E111" s="58"/>
       <c r="F111" s="48">
         <f>100-0.015</f>
         <v>99.984999999999999</v>
@@ -3274,7 +3249,7 @@
     </row>
     <row r="113" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B113" s="18"/>
       <c r="C113" s="18"/>
@@ -3283,50 +3258,50 @@
       <c r="F113" s="21"/>
     </row>
     <row r="114" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="B114" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C114" s="53"/>
-      <c r="D114" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="E114" s="53"/>
-      <c r="F114" s="53" t="s">
-        <v>158</v>
-      </c>
-      <c r="G114" s="53"/>
+      <c r="A114" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" s="57"/>
+      <c r="D114" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="E114" s="57"/>
+      <c r="F114" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="G114" s="57"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="53"/>
-      <c r="B115" s="53"/>
-      <c r="C115" s="53"/>
-      <c r="D115" s="53"/>
-      <c r="E115" s="53"/>
+      <c r="A115" s="57"/>
+      <c r="B115" s="57"/>
+      <c r="C115" s="57"/>
+      <c r="D115" s="57"/>
+      <c r="E115" s="57"/>
       <c r="F115" s="43" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G115" s="43" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B116" s="22">
         <v>1</v>
       </c>
-      <c r="C116" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="D116" s="83" t="s">
-        <v>107</v>
-      </c>
-      <c r="E116" s="64" t="s">
-        <v>145</v>
+      <c r="C116" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="D116" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="E116" s="58" t="s">
+        <v>142</v>
       </c>
       <c r="F116" s="40">
         <f>1-0.00015</f>
@@ -3339,16 +3314,16 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B117" s="22">
         <v>10</v>
       </c>
-      <c r="C117" s="64"/>
-      <c r="D117" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="E117" s="64"/>
+      <c r="C117" s="58"/>
+      <c r="D117" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="E117" s="58"/>
       <c r="F117" s="47">
         <f>10-0.0041</f>
         <v>9.9959000000000007</v>
@@ -3360,16 +3335,16 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B118" s="22">
         <v>100</v>
       </c>
-      <c r="C118" s="64"/>
-      <c r="D118" s="83" t="s">
-        <v>109</v>
-      </c>
-      <c r="E118" s="64"/>
+      <c r="C118" s="58"/>
+      <c r="D118" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="E118" s="58"/>
       <c r="F118" s="48">
         <f>100-0.081</f>
         <v>99.918999999999997</v>
@@ -3388,47 +3363,164 @@
       <c r="F119" s="16"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B120" s="50"/>
+      <c r="A120" s="78" t="s">
+        <v>158</v>
+      </c>
+      <c r="B120" s="78"/>
       <c r="C120" s="42" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D120" s="10"/>
       <c r="E120" s="10"/>
       <c r="F120" s="16"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="50" t="s">
-        <v>163</v>
-      </c>
-      <c r="B121" s="50"/>
+      <c r="A121" s="78" t="s">
+        <v>160</v>
+      </c>
+      <c r="B121" s="78"/>
       <c r="C121" s="30"/>
       <c r="D121" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E121" s="85" t="s">
-        <v>47</v>
-      </c>
-      <c r="F121" s="51"/>
+        <v>44</v>
+      </c>
+      <c r="F121" s="86"/>
       <c r="G121" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H121" s="32"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" s="50"/>
-      <c r="C122" s="86" t="s">
-        <v>48</v>
-      </c>
-      <c r="D122" s="86"/>
+      <c r="A122" s="78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122" s="78"/>
+      <c r="C122" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="141">
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="A54:A61"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="C55:C61"/>
+    <mergeCell ref="F55:F61"/>
+    <mergeCell ref="B56:B61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="F62:F64"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="F90:F92"/>
+    <mergeCell ref="B80:C81"/>
+    <mergeCell ref="E80:F81"/>
+    <mergeCell ref="F65:F67"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="F93:F94"/>
+    <mergeCell ref="F87:F89"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C35:C43"/>
+    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="E35:E43"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="E116:E118"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="C87:C89"/>
+    <mergeCell ref="C99:D100"/>
+    <mergeCell ref="E99:F100"/>
+    <mergeCell ref="B114:C115"/>
+    <mergeCell ref="D114:E115"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="B106:C107"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A114:A115"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A80:A81"/>
@@ -3453,123 +3545,6 @@
     <mergeCell ref="G95:G96"/>
     <mergeCell ref="H93:H94"/>
     <mergeCell ref="G93:G94"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C116:C118"/>
-    <mergeCell ref="E116:E118"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="D86:D88"/>
-    <mergeCell ref="C87:C89"/>
-    <mergeCell ref="C99:D100"/>
-    <mergeCell ref="E99:F100"/>
-    <mergeCell ref="B114:C115"/>
-    <mergeCell ref="D114:E115"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="B106:C107"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C35:C43"/>
-    <mergeCell ref="D31:E32"/>
-    <mergeCell ref="E35:E43"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="E46:F47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="F95:F96"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="F93:F94"/>
-    <mergeCell ref="F87:F89"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="E121:F121"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="F48:F50"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="A54:A61"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="C55:C61"/>
-    <mergeCell ref="F55:F61"/>
-    <mergeCell ref="B56:B61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="F62:F64"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="F90:F92"/>
-    <mergeCell ref="B80:C81"/>
-    <mergeCell ref="E80:F81"/>
-    <mergeCell ref="F65:F67"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.59614583333333337" header="0.39370078740157483" footer="0.39370078740157483"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
